--- a/data/trans_orig/KIDMED_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/KIDMED_R2-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1195</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5612</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10,45%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>526</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2515</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2976</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1258</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4814</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>299</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5716</t>
+          <t>6507</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -833,74 +833,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>52520</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>48103</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,77%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>89,55%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>53173</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>51184</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>99,02%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,32%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>45309</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>42929</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>45905</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>98,7%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>93,52%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>57087</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>53531</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>58345</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,84%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>91,75%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>141</t>
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>110259</t>
+          <t>97829</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>106327</t>
+          <t>93113</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>111612</t>
+          <t>99321</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>14003</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8371</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>22744</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,88%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>11438</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6524</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>18070</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,0%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15661</t>
+          <t>11825</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8993</t>
+          <t>7024</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25686</t>
+          <t>17772</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,22 +1138,22 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>27099</t>
+          <t>25828</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18619</t>
+          <t>17350</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37792</t>
+          <t>35696</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>611</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>452420</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>443679</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>458052</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,12%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,21%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>608</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>440394</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>433762</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>445308</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>97,47%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,56%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>611</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>489589</t>
+          <t>412841</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>479564</t>
+          <t>406894</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>496257</t>
+          <t>417642</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>929983</t>
+          <t>865262</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>919290</t>
+          <t>855394</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>938463</t>
+          <t>873740</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>625</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7173</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3364</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12834</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4591</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1559</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9186</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,28%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7611</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t>1601</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13559</t>
+          <t>9824</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>12201</t>
+          <t>12000</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7393</t>
+          <t>6731</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20417</t>
+          <t>19664</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>159513</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>153852</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>163322</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>95,7%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>92,3%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,98%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>141595</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>137000</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>144627</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>96,86%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>93,72%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,93%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>173528</t>
+          <t>142312</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>167580</t>
+          <t>137316</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>177751</t>
+          <t>145539</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>315123</t>
+          <t>301825</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>306907</t>
+          <t>294161</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>319931</t>
+          <t>307094</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>22371</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>14389</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>31658</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,61%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>16554</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>10994</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>24584</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,77%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24530</t>
+          <t>17249</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16282</t>
+          <t>11005</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35530</t>
+          <t>25426</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>41084</t>
+          <t>39620</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30791</t>
+          <t>29610</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54605</t>
+          <t>51442</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>664453</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>655166</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>672435</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,74%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,39%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,9%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>890</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>635163</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>627133</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>640723</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>97,46%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,23%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,31%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>720203</t>
+          <t>600462</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>709203</t>
+          <t>592285</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>728451</t>
+          <t>606706</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1355366</t>
+          <t>1264915</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1341845</t>
+          <t>1253093</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1365659</t>
+          <t>1274925</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
